--- a/data/references/Broedvogels_Datums.xlsx
+++ b/data/references/Broedvogels_Datums.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Documents\Soortenbehoud\arpl\data\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="673">
   <si>
     <t>Pagina</t>
   </si>
@@ -798,18 +798,6 @@
     <t>Kluut x x x . x . 1 1 . . 5 mei-5 jun 1000</t>
   </si>
   <si>
-    <t>Kluut D D</t>
-  </si>
-  <si>
-    <t>1 mei-5 jun</t>
-  </si>
-  <si>
-    <t>Kluut x x x . . . 1 1 D D 1 mei-5 jun 500</t>
-  </si>
-  <si>
-    <t>Kievit x*</t>
-  </si>
-  <si>
     <t>Kievit x x x x 2 1 x* . 25 mrt-10 mei 1000</t>
   </si>
   <si>
@@ -849,9 +837,6 @@
     <t>Wulp x x . x x 2 1 x . 10 mrt-31 mei 1000</t>
   </si>
   <si>
-    <t>Grutto x*</t>
-  </si>
-  <si>
     <t>Grutto x x x x x 2 1 x* . 25 mrt-10 mei 1000</t>
   </si>
   <si>
@@ -903,9 +888,6 @@
     <t>Tureluur x x . . x 2 1 x . 15 apr-10 jun 1000</t>
   </si>
   <si>
-    <t>Kokmeeuw D D</t>
-  </si>
-  <si>
     <t>1 mei-15 jun</t>
   </si>
   <si>
@@ -921,18 +903,12 @@
     <t>Dwergmeeuw x x x . x x 2 2 x x 15 mei-15 jun 1000</t>
   </si>
   <si>
-    <t>Zwartkopmeeuw D D</t>
-  </si>
-  <si>
     <t>1 mei-30 jun</t>
   </si>
   <si>
     <t>Zwartkopmeeuw x x x . x x 1 1 D D 1 mei-30 jun 500</t>
   </si>
   <si>
-    <t>Stormmeeuw D D</t>
-  </si>
-  <si>
     <t>Stormmeeuw x x x . x x 1 1 D D 1 mei-15 jun 500</t>
   </si>
   <si>
@@ -942,9 +918,6 @@
     <t>Grote Mantelmeeuw x x x . x x 2 1 x x 15 mei-15 jun 1000</t>
   </si>
   <si>
-    <t>Zilvermeeuw D D</t>
-  </si>
-  <si>
     <t>Zilvermeeuw x x x . x x 1 1 D D 1 mei-15 jun 500</t>
   </si>
   <si>
@@ -963,9 +936,6 @@
     <t>Geelpootmeeuw x x x . x x 2 2 x x 15 mei-15 jun 1000</t>
   </si>
   <si>
-    <t>Kleine Mantelmeeuw D D</t>
-  </si>
-  <si>
     <t>Kleine Mantelmeeuw x x x . x x 1 1 D D 1 mei-15 jun 500</t>
   </si>
   <si>
@@ -978,9 +948,6 @@
     <t>Lachstern x x x . x x 2 2 x . 15 mei-30 jun 1000</t>
   </si>
   <si>
-    <t>Grote Stern D D</t>
-  </si>
-  <si>
     <t>Grote Stern x x x . x x 1 1 D D 1 mei-15 jun 500</t>
   </si>
   <si>
@@ -999,9 +966,6 @@
     <t>Witvleugelstern x x x . . x 2 2 x x 25 mei-30 jun 1000</t>
   </si>
   <si>
-    <t>Zwarte Stern D D</t>
-  </si>
-  <si>
     <t>Zwarte Stern x x x . x x 1 1 D D 15 mei-30 jun 500</t>
   </si>
   <si>
@@ -1320,9 +1284,6 @@
     <t>Huiskraai x x x . x x 2 2 x . 25 mrt-15 jul 2500</t>
   </si>
   <si>
-    <t>Roek D</t>
-  </si>
-  <si>
     <t>Roek x x x . . . 1 1 . D 10 mrt-10 mei 500</t>
   </si>
   <si>
@@ -1425,9 +1386,6 @@
     <t>Veldleeuwerik x x . x x 1 1 x . 25 mrt-10 jun 300</t>
   </si>
   <si>
-    <t>Oeverzwaluw D</t>
-  </si>
-  <si>
     <t>15 mei-10 jul</t>
   </si>
   <si>
@@ -1440,9 +1398,6 @@
     <t>Boerenzwaluw x x x x 2 2 x . 10 mei-20 jun 1000</t>
   </si>
   <si>
-    <t>Huiszwaluw D</t>
-  </si>
-  <si>
     <t>10 jun-10 aug</t>
   </si>
   <si>
@@ -2047,6 +2002,42 @@
   </si>
   <si>
     <t>20 apr-31 jul</t>
+  </si>
+  <si>
+    <t>Grutto</t>
+  </si>
+  <si>
+    <t>Kievit</t>
+  </si>
+  <si>
+    <t>Kokmeeuw</t>
+  </si>
+  <si>
+    <t>Zwartkopmeeuw</t>
+  </si>
+  <si>
+    <t>Zilvermeeuw</t>
+  </si>
+  <si>
+    <t>Stormmeeuw</t>
+  </si>
+  <si>
+    <t>Kleine Mantelmeeuw</t>
+  </si>
+  <si>
+    <t>Grote Stern</t>
+  </si>
+  <si>
+    <t>Zwarte Stern</t>
+  </si>
+  <si>
+    <t>Roek</t>
+  </si>
+  <si>
+    <t>Oeverzwaluw</t>
+  </si>
+  <si>
+    <t>Huiszwaluw</t>
   </si>
 </sst>
 </file>
@@ -2479,7 +2470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J263"/>
+  <dimension ref="A1:J262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3595,7 +3586,7 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="7" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="I37" s="10">
         <v>2500</v>
@@ -5393,61 +5384,61 @@
       </c>
     </row>
     <row r="98" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="7">
+      <c r="A98" s="2">
         <v>45</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I98" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C98" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="7" t="s">
+    </row>
+    <row r="99" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="7">
+        <v>45</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="I98" s="10">
-        <v>500</v>
-      </c>
-      <c r="J98" s="11" t="s">
+      <c r="C99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I99" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J99" s="11" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>45</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I99" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5455,7 +5446,7 @@
         <v>45</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>11</v>
@@ -5469,13 +5460,13 @@
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="7" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="I100" s="10">
         <v>1000</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5483,207 +5474,207 @@
         <v>45</v>
       </c>
       <c r="B101" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="I101" s="10">
         <v>1000</v>
       </c>
       <c r="J101" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>45</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="7">
+      <c r="C102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I102" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="7">
         <v>45</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H102" s="7" t="s">
+      <c r="B103" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="I102" s="10">
+      <c r="C103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="I103" s="10">
         <v>1000</v>
       </c>
-      <c r="J102" s="11" t="s">
+      <c r="J103" s="11" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
+    <row r="104" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
         <v>45</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B104" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I104" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J104" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I103" s="5">
+    </row>
+    <row r="105" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="7">
+        <v>45</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I105" s="10">
         <v>1000</v>
       </c>
-      <c r="J103" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="7">
+      <c r="J105" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
         <v>45</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I104" s="10">
+      <c r="B106" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I106" s="5">
         <v>1000</v>
       </c>
-      <c r="J104" s="11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
+      <c r="J106" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="7">
         <v>45</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I105" s="5">
+      <c r="B107" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="I107" s="10">
         <v>1000</v>
       </c>
-      <c r="J105" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="7">
-        <v>45</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I106" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
-        <v>45</v>
-      </c>
-      <c r="B107" s="3" t="s">
+      <c r="J107" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I107" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5691,7 +5682,7 @@
         <v>45</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C108" s="9" t="s">
         <v>11</v>
@@ -5705,13 +5696,13 @@
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
       <c r="H108" s="7" t="s">
-        <v>284</v>
+        <v>70</v>
       </c>
       <c r="I108" s="10">
         <v>1000</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5719,7 +5710,7 @@
         <v>45</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C109" s="9" t="s">
         <v>11</v>
@@ -5733,41 +5724,41 @@
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="7" t="s">
-        <v>70</v>
+        <v>285</v>
       </c>
       <c r="I109" s="10">
         <v>1000</v>
       </c>
       <c r="J109" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>45</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J110" s="6" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="7">
-        <v>45</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="I110" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J110" s="11" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5775,7 +5766,7 @@
         <v>45</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>292</v>
+        <v>663</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>11</v>
@@ -5783,819 +5774,819 @@
       <c r="D111" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="4"/>
+      <c r="E111" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="I111" s="5">
+        <v>500</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="7">
+        <v>45</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="I112" s="10">
         <v>1000</v>
       </c>
-      <c r="J111" s="6" t="s">
+      <c r="J112" s="11" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
+    <row r="113" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
         <v>45</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B113" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C112" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H112" s="2" t="s">
+      <c r="I113" s="5">
+        <v>500</v>
+      </c>
+      <c r="J113" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I112" s="5">
+    </row>
+    <row r="114" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="7">
+        <v>45</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I114" s="10">
         <v>500</v>
       </c>
-      <c r="J112" s="6" t="s">
+      <c r="J114" s="11" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="7">
+    <row r="115" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
         <v>45</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B115" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C113" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" s="9"/>
-      <c r="G113" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H113" s="7" t="s">
+      <c r="C115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I115" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J115" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="I113" s="10">
+    </row>
+    <row r="116" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="7">
+        <v>45</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I116" s="10">
+        <v>500</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>45</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I117" s="5">
         <v>1000</v>
       </c>
-      <c r="J113" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="2">
-        <v>45</v>
-      </c>
-      <c r="B114" s="3" t="s">
+      <c r="J117" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="7">
+        <v>46</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="I118" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I119" s="5">
+        <v>500</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="7">
+        <v>46</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="9"/>
+      <c r="G120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="I120" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I121" s="5">
+        <v>500</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="7">
+        <v>46</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="9"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="I122" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I123" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="7">
+        <v>46</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="9"/>
+      <c r="G124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="I124" s="10">
+        <v>500</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="4"/>
+      <c r="H125" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I125" s="5">
         <v>300</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I114" s="5">
+      <c r="J125" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="7">
+        <v>46</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="9"/>
+      <c r="H126" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I126" s="10">
+        <v>300</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="4"/>
+      <c r="H127" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I127" s="5">
+        <v>300</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="7">
+        <v>46</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="9"/>
+      <c r="G128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I128" s="10">
+        <v>300</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>46</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="4"/>
+      <c r="H129" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I129" s="5">
+        <v>300</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="7">
+        <v>46</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="I130" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>46</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I131" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="7">
+        <v>46</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="9"/>
+      <c r="G132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="I132" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>46</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="4"/>
+      <c r="G133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I133" s="5">
+        <v>2500</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="7">
+        <v>46</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="I134" s="10">
         <v>500</v>
       </c>
-      <c r="J114" s="6" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="7">
-        <v>45</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="9"/>
-      <c r="G115" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="I115" s="10">
+      <c r="J134" s="11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>46</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I135" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J135" s="6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="7">
+        <v>46</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I136" s="10">
         <v>500</v>
       </c>
-      <c r="J115" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
-        <v>45</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I116" s="5">
+      <c r="J136" s="11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>46</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="4"/>
+      <c r="G137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I137" s="5">
         <v>1000</v>
       </c>
-      <c r="J116" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="7">
-        <v>45</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="I117" s="10">
+      <c r="J137" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="7">
+        <v>46</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="I138" s="10">
         <v>500</v>
       </c>
-      <c r="J117" s="11" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="2">
-        <v>45</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I118" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="7">
-        <v>46</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I119" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J119" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
-        <v>46</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I120" s="5">
-        <v>500</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="7">
-        <v>46</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C121" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="I121" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J121" s="11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
-        <v>46</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I122" s="5">
-        <v>500</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="7">
-        <v>46</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="C123" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="I123" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="2">
-        <v>46</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I124" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J124" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="7">
-        <v>46</v>
-      </c>
-      <c r="B125" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="I125" s="10">
-        <v>500</v>
-      </c>
-      <c r="J125" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2">
-        <v>46</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G126" s="4"/>
-      <c r="H126" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="I126" s="5">
-        <v>300</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="7">
-        <v>46</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C127" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G127" s="9"/>
-      <c r="H127" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="I127" s="10">
-        <v>300</v>
-      </c>
-      <c r="J127" s="11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="2">
-        <v>46</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G128" s="4"/>
-      <c r="H128" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I128" s="5">
-        <v>300</v>
-      </c>
-      <c r="J128" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="7">
-        <v>46</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C129" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I129" s="10">
-        <v>300</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="2">
-        <v>46</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G130" s="4"/>
-      <c r="H130" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="I130" s="5">
-        <v>300</v>
-      </c>
-      <c r="J130" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7">
-        <v>46</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I131" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J131" s="11" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="2">
-        <v>46</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="4"/>
-      <c r="G132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I132" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J132" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="7">
-        <v>46</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="C133" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="I133" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J133" s="11" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="2">
-        <v>46</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" s="4"/>
-      <c r="G134" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="I134" s="5">
-        <v>2500</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="7">
-        <v>46</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="C135" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G135" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H135" s="7" t="s">
+      <c r="J138" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="I135" s="10">
-        <v>500</v>
-      </c>
-      <c r="J135" s="11" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="2">
-        <v>46</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="I136" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J136" s="6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="7">
-        <v>46</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="C137" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G137" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="I137" s="10">
-        <v>500</v>
-      </c>
-      <c r="J137" s="11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="2">
-        <v>46</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="I138" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J138" s="6" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6603,361 +6594,365 @@
         <v>46</v>
       </c>
       <c r="B139" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="I139" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J139" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>46</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="4"/>
+      <c r="G140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I140" s="5">
+        <v>300</v>
+      </c>
+      <c r="J140" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="7">
+        <v>46</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G141" s="9"/>
+      <c r="H141" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I141" s="10">
+        <v>2500</v>
+      </c>
+      <c r="J141" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>46</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H142" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C139" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D139" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H139" s="7" t="s">
+      <c r="I142" s="5">
+        <v>2000</v>
+      </c>
+      <c r="J142" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="I139" s="10">
+    </row>
+    <row r="143" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="7">
+        <v>46</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="I143" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <v>46</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="I144" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="7">
+        <v>46</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="I145" s="10">
         <v>500</v>
       </c>
-      <c r="J139" s="11" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="7">
+      <c r="J145" s="11" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
         <v>46</v>
       </c>
-      <c r="B140" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="C140" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G140" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="I140" s="10">
+      <c r="B146" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I146" s="5">
+        <v>500</v>
+      </c>
+      <c r="J146" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="7">
+        <v>46</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="I147" s="10">
+        <v>300</v>
+      </c>
+      <c r="J147" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>46</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G148" s="4"/>
+      <c r="H148" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I148" s="5">
+        <v>500</v>
+      </c>
+      <c r="J148" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="7">
+        <v>46</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="I149" s="10">
         <v>1000</v>
       </c>
-      <c r="J140" s="11" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="2">
+      <c r="J149" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
         <v>46</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="I141" s="5">
-        <v>300</v>
-      </c>
-      <c r="J141" s="6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="7">
-        <v>46</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="C142" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G142" s="9"/>
-      <c r="H142" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I142" s="10">
-        <v>2500</v>
-      </c>
-      <c r="J142" s="11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="2">
-        <v>46</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="I143" s="5">
-        <v>2000</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="7">
-        <v>46</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="C144" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G144" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="I144" s="10">
+      <c r="B150" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I150" s="5">
         <v>1000</v>
       </c>
-      <c r="J144" s="11" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="2">
-        <v>46</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="I145" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J145" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="7">
-        <v>46</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="C146" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D146" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="I146" s="10">
-        <v>500</v>
-      </c>
-      <c r="J146" s="11" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="2">
-        <v>46</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="4"/>
-      <c r="G147" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H147" s="2" t="s">
+      <c r="J150" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="I147" s="5">
-        <v>500</v>
-      </c>
-      <c r="J147" s="6" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="7">
-        <v>46</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C148" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G148" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="I148" s="10">
-        <v>300</v>
-      </c>
-      <c r="J148" s="11" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="2">
-        <v>46</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G149" s="4"/>
-      <c r="H149" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I149" s="5">
-        <v>500</v>
-      </c>
-      <c r="J149" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7">
-        <v>46</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="C150" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D150" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F150" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G150" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="I150" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J150" s="11" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6965,7 +6960,7 @@
         <v>46</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>11</v>
@@ -6976,20 +6971,18 @@
       <c r="E151" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F151" s="4"/>
       <c r="G151" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="I151" s="5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6997,179 +6990,179 @@
         <v>46</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152" s="4"/>
+      <c r="H152" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I152" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J152" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="7">
+        <v>46</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153" s="9"/>
+      <c r="H153" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I153" s="10">
+        <v>2500</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>46</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I154" s="5">
+        <v>500</v>
+      </c>
+      <c r="J154" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="7">
+        <v>47</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="9"/>
+      <c r="G155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="I155" s="10">
+        <v>500</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>47</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="4"/>
+      <c r="G156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I156" s="5">
+        <v>500</v>
+      </c>
+      <c r="J156" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="C152" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I152" s="5">
+    </row>
+    <row r="157" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="7">
+        <v>47</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="9"/>
+      <c r="G157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="I157" s="10">
         <v>500</v>
       </c>
-      <c r="J152" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="2">
-        <v>46</v>
-      </c>
-      <c r="B153" s="3" t="s">
+      <c r="J157" s="11" t="s">
         <v>403</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G153" s="4"/>
-      <c r="H153" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="I153" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J153" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="7">
-        <v>46</v>
-      </c>
-      <c r="B154" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="C154" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D154" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E154" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F154" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G154" s="9"/>
-      <c r="H154" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I154" s="10">
-        <v>2500</v>
-      </c>
-      <c r="J154" s="11" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="2">
-        <v>46</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="I155" s="5">
-        <v>500</v>
-      </c>
-      <c r="J155" s="6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="7">
-        <v>47</v>
-      </c>
-      <c r="B156" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="C156" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D156" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="I156" s="10">
-        <v>500</v>
-      </c>
-      <c r="J156" s="11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="2">
-        <v>47</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F157" s="4"/>
-      <c r="G157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H157" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I157" s="5">
-        <v>500</v>
-      </c>
-      <c r="J157" s="6" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7177,7 +7170,7 @@
         <v>47</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C158" s="9" t="s">
         <v>11</v>
@@ -7185,639 +7178,639 @@
       <c r="D158" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E158" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F158" s="9"/>
+      <c r="E158" s="9"/>
+      <c r="F158" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="G158" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="I158" s="10">
         <v>500</v>
       </c>
       <c r="J158" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>47</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G159" s="4"/>
+      <c r="H159" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I159" s="5">
+        <v>500</v>
+      </c>
+      <c r="J159" s="6" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="7">
+        <v>47</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C160" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="9"/>
+      <c r="E160" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G160" s="9"/>
+      <c r="H160" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I160" s="10">
+        <v>300</v>
+      </c>
+      <c r="J160" s="11" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>47</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I161" s="5">
+        <v>500</v>
+      </c>
+      <c r="J161" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="7">
+        <v>47</v>
+      </c>
+      <c r="B162" s="8" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="7">
+      <c r="C162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="9"/>
+      <c r="E162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="9"/>
+      <c r="H162" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="I162" s="10">
+        <v>300</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
         <v>47</v>
       </c>
-      <c r="B159" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="C159" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="9"/>
-      <c r="F159" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="I159" s="10">
+      <c r="B163" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="4"/>
+      <c r="G163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="I163" s="5">
+        <v>2500</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="7">
+        <v>47</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="9"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="I164" s="10">
         <v>500</v>
       </c>
-      <c r="J159" s="11" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="2">
+      <c r="J164" s="11" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
         <v>47</v>
       </c>
-      <c r="B160" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G160" s="4"/>
-      <c r="H160" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="I160" s="5">
+      <c r="B165" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="4"/>
+      <c r="H165" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I165" s="5">
         <v>500</v>
       </c>
-      <c r="J160" s="6" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="7">
+      <c r="J165" s="6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="7">
         <v>47</v>
       </c>
-      <c r="B161" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C161" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G161" s="9"/>
-      <c r="H161" s="7" t="s">
+      <c r="B166" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="I166" s="10">
+        <v>500</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>47</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="I167" s="5">
+        <v>1500</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="7">
+        <v>47</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="9"/>
+      <c r="F168" s="9"/>
+      <c r="G168" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="I168" s="10">
+        <v>300</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>47</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I169" s="5">
+        <v>300</v>
+      </c>
+      <c r="J169" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="7">
+        <v>47</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="9"/>
+      <c r="F170" s="9"/>
+      <c r="G170" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="I170" s="10">
+        <v>300</v>
+      </c>
+      <c r="J170" s="11" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>47</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H171" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I161" s="10">
+      <c r="I171" s="5">
         <v>300</v>
       </c>
-      <c r="J161" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="2">
+      <c r="J171" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="7">
         <v>47</v>
       </c>
-      <c r="B162" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F162" s="4"/>
-      <c r="G162" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H162" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="I162" s="5">
+      <c r="B172" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="9"/>
+      <c r="E172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172" s="9"/>
+      <c r="H172" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I172" s="10">
+        <v>300</v>
+      </c>
+      <c r="J172" s="11" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>47</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="4"/>
+      <c r="H173" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I173" s="5">
+        <v>300</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="7">
+        <v>47</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I174" s="10">
         <v>500</v>
       </c>
-      <c r="J162" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="7">
+      <c r="J174" s="11" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
         <v>47</v>
       </c>
-      <c r="B163" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="C163" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G163" s="9"/>
-      <c r="H163" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="I163" s="10">
+      <c r="B175" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="I175" s="5">
+        <v>500</v>
+      </c>
+      <c r="J175" s="6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="7">
+        <v>47</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="9"/>
+      <c r="G176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="I176" s="10">
         <v>300</v>
       </c>
-      <c r="J163" s="11" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="2">
+      <c r="J176" s="11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
         <v>47</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F164" s="4"/>
-      <c r="G164" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H164" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="I164" s="5">
-        <v>2500</v>
-      </c>
-      <c r="J164" s="6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="7">
+      <c r="B177" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I177" s="5">
+        <v>300</v>
+      </c>
+      <c r="J177" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="7">
         <v>47</v>
       </c>
-      <c r="B165" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="C165" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D165" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F165" s="9"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="I165" s="10">
+      <c r="B178" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="I178" s="10">
         <v>500</v>
       </c>
-      <c r="J165" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="2">
+      <c r="J178" s="11" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
         <v>47</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G166" s="4"/>
-      <c r="H166" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I166" s="5">
-        <v>500</v>
-      </c>
-      <c r="J166" s="6" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="7">
-        <v>47</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="C167" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H167" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="I167" s="10">
-        <v>500</v>
-      </c>
-      <c r="J167" s="11" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="2">
-        <v>47</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H168" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="I168" s="5">
-        <v>1500</v>
-      </c>
-      <c r="J168" s="6" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="7">
-        <v>47</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H169" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="I169" s="10">
-        <v>300</v>
-      </c>
-      <c r="J169" s="11" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="2">
-        <v>47</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G170" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H170" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I170" s="5">
-        <v>300</v>
-      </c>
-      <c r="J170" s="6" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7">
-        <v>47</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="C171" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="9"/>
-      <c r="F171" s="9"/>
-      <c r="G171" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="I171" s="10">
-        <v>300</v>
-      </c>
-      <c r="J171" s="11" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="2">
-        <v>47</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="4"/>
-      <c r="F172" s="4"/>
-      <c r="G172" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H172" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I172" s="5">
-        <v>300</v>
-      </c>
-      <c r="J172" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="7">
-        <v>47</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G173" s="9"/>
-      <c r="H173" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I173" s="10">
-        <v>300</v>
-      </c>
-      <c r="J173" s="11" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="2">
-        <v>47</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G174" s="4"/>
-      <c r="H174" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I174" s="5">
-        <v>300</v>
-      </c>
-      <c r="J174" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="7">
-        <v>47</v>
-      </c>
-      <c r="B175" s="8" t="s">
+      <c r="B179" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="C175" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I175" s="10">
-        <v>500</v>
-      </c>
-      <c r="J175" s="11" t="s">
+      <c r="C179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G179" s="4"/>
+      <c r="H179" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I179" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J179" s="6" t="s">
         <v>458</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="2">
-        <v>47</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F176" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G176" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H176" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="I176" s="5">
-        <v>500</v>
-      </c>
-      <c r="J176" s="6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="7">
-        <v>47</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E177" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="I177" s="10">
-        <v>300</v>
-      </c>
-      <c r="J177" s="11" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="2">
-        <v>47</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G178" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="I178" s="5">
-        <v>300</v>
-      </c>
-      <c r="J178" s="6" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="7">
-        <v>47</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E179" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="I179" s="10">
-        <v>500</v>
-      </c>
-      <c r="J179" s="11" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7825,7 +7818,7 @@
         <v>47</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>471</v>
+        <v>672</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>11</v>
@@ -7836,846 +7829,846 @@
       <c r="E180" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F180" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="2" t="s">
-        <v>98</v>
+        <v>459</v>
       </c>
       <c r="I180" s="5">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="J180" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="7">
+        <v>47</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="I181" s="10">
+        <v>300</v>
+      </c>
+      <c r="J181" s="11" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>47</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I182" s="5">
+        <v>500</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="7">
+        <v>47</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I183" s="10">
+        <v>200</v>
+      </c>
+      <c r="J183" s="11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>47</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I184" s="5">
+        <v>300</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="7">
+        <v>47</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="9"/>
+      <c r="H185" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I185" s="10">
+        <v>100</v>
+      </c>
+      <c r="J185" s="11" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="2">
+    <row r="186" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
         <v>47</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B186" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C181" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" s="4"/>
-      <c r="G181" s="4"/>
-      <c r="H181" s="2" t="s">
+      <c r="C186" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="4"/>
+      <c r="H186" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I181" s="5">
+      <c r="I186" s="5">
+        <v>200</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="7">
+        <v>47</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="I187" s="10">
         <v>300</v>
       </c>
-      <c r="J181" s="6" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="7">
+      <c r="J187" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
         <v>47</v>
       </c>
-      <c r="B182" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D182" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="7" t="s">
+      <c r="B188" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I182" s="10">
+      <c r="I188" s="5">
         <v>300</v>
       </c>
-      <c r="J182" s="11" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="2">
+      <c r="J188" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="7">
         <v>47</v>
       </c>
-      <c r="B183" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D183" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="4"/>
-      <c r="F183" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G183" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H183" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I183" s="5">
+      <c r="B189" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="I189" s="10">
+        <v>300</v>
+      </c>
+      <c r="J189" s="11" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>47</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I190" s="5">
+        <v>300</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="7">
+        <v>47</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I191" s="10">
+        <v>200</v>
+      </c>
+      <c r="J191" s="11" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="2">
+        <v>47</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I192" s="5">
+        <v>300</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="7">
+        <v>47</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I193" s="10">
+        <v>300</v>
+      </c>
+      <c r="J193" s="11" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>47</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="4"/>
+      <c r="H194" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="I194" s="5">
+        <v>100</v>
+      </c>
+      <c r="J194" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="7">
+        <v>47</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
+      <c r="F195" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" s="9"/>
+      <c r="H195" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I195" s="10">
+        <v>100</v>
+      </c>
+      <c r="J195" s="11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
+        <v>47</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
+      <c r="H196" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I196" s="5">
+        <v>300</v>
+      </c>
+      <c r="J196" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="J183" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="7">
+    </row>
+    <row r="197" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="7">
         <v>47</v>
       </c>
-      <c r="B184" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D184" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H184" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I184" s="10">
+      <c r="B197" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="I197" s="10">
         <v>200</v>
       </c>
-      <c r="J184" s="11" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="2">
-        <v>47</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D185" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I185" s="5">
+      <c r="J197" s="11" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="2">
+        <v>48</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="I198" s="5">
+        <v>200</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="7">
+        <v>48</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="I199" s="10">
         <v>300</v>
       </c>
-      <c r="J185" s="6" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="7">
-        <v>47</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G186" s="9"/>
-      <c r="H186" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I186" s="10">
+      <c r="J199" s="11" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="2">
+        <v>48</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I200" s="5">
+        <v>200</v>
+      </c>
+      <c r="J200" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="7">
+        <v>48</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F201" s="9"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="I201" s="10">
+        <v>300</v>
+      </c>
+      <c r="J201" s="11" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="2">
+        <v>48</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="4"/>
+      <c r="H202" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I202" s="5">
+        <v>200</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="7">
+        <v>48</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="9"/>
+      <c r="H203" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I203" s="10">
+        <v>200</v>
+      </c>
+      <c r="J203" s="11" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="2">
+        <v>48</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4"/>
+      <c r="G204" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="I204" s="5">
+        <v>300</v>
+      </c>
+      <c r="J204" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="7">
+        <v>48</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="I205" s="10">
+        <v>200</v>
+      </c>
+      <c r="J205" s="11" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="2">
+        <v>48</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F206" s="4"/>
+      <c r="G206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="I206" s="5">
+        <v>300</v>
+      </c>
+      <c r="J206" s="6" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="7">
+        <v>48</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="9"/>
+      <c r="F207" s="9"/>
+      <c r="G207" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I207" s="10">
+        <v>200</v>
+      </c>
+      <c r="J207" s="11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
+        <v>48</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="4"/>
+      <c r="H208" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="I208" s="5">
         <v>100</v>
       </c>
-      <c r="J186" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="2">
-        <v>47</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G187" s="4"/>
-      <c r="H187" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="I187" s="5">
+      <c r="J208" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="7">
+        <v>48</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
+      <c r="F209" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="9"/>
+      <c r="H209" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I209" s="10">
         <v>200</v>
       </c>
-      <c r="J187" s="6" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="7">
-        <v>47</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="I188" s="10">
+      <c r="J209" s="11" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="2">
+        <v>48</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I210" s="5">
         <v>300</v>
       </c>
-      <c r="J188" s="11" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="2">
-        <v>47</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D189" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="I189" s="5">
-        <v>300</v>
-      </c>
-      <c r="J189" s="6" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="7">
-        <v>47</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D190" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="I190" s="10">
-        <v>300</v>
-      </c>
-      <c r="J190" s="11" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="2">
-        <v>47</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="I191" s="5">
-        <v>300</v>
-      </c>
-      <c r="J191" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="7">
-        <v>47</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="C192" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D192" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="I192" s="10">
-        <v>200</v>
-      </c>
-      <c r="J192" s="11" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="2">
-        <v>47</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I193" s="5">
-        <v>300</v>
-      </c>
-      <c r="J193" s="6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="7">
-        <v>47</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D194" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F194" s="9"/>
-      <c r="G194" s="9"/>
-      <c r="H194" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="I194" s="10">
-        <v>300</v>
-      </c>
-      <c r="J194" s="11" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="2">
-        <v>47</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G195" s="4"/>
-      <c r="H195" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="I195" s="5">
-        <v>100</v>
-      </c>
-      <c r="J195" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="7">
-        <v>47</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G196" s="9"/>
-      <c r="H196" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I196" s="10">
-        <v>100</v>
-      </c>
-      <c r="J196" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="2">
-        <v>47</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I197" s="5">
-        <v>300</v>
-      </c>
-      <c r="J197" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="7">
-        <v>47</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D198" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H198" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="I198" s="10">
-        <v>200</v>
-      </c>
-      <c r="J198" s="11" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="2">
-        <v>48</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D199" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="I199" s="5">
-        <v>200</v>
-      </c>
-      <c r="J199" s="6" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="7">
-        <v>48</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D200" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="I200" s="10">
-        <v>300</v>
-      </c>
-      <c r="J200" s="11" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="2">
-        <v>48</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D201" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="I201" s="5">
-        <v>200</v>
-      </c>
-      <c r="J201" s="6" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="7">
-        <v>48</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D202" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E202" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F202" s="9"/>
-      <c r="G202" s="9"/>
-      <c r="H202" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="I202" s="10">
-        <v>300</v>
-      </c>
-      <c r="J202" s="11" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="2">
-        <v>48</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D203" s="4"/>
-      <c r="E203" s="4"/>
-      <c r="F203" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G203" s="4"/>
-      <c r="H203" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I203" s="5">
-        <v>200</v>
-      </c>
-      <c r="J203" s="6" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="7">
-        <v>48</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G204" s="9"/>
-      <c r="H204" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I204" s="10">
-        <v>200</v>
-      </c>
-      <c r="J204" s="11" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="2">
-        <v>48</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="I205" s="5">
-        <v>300</v>
-      </c>
-      <c r="J205" s="6" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="7">
-        <v>48</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D206" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9"/>
-      <c r="G206" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H206" s="7" t="s">
+      <c r="J210" s="6" t="s">
         <v>536</v>
-      </c>
-      <c r="I206" s="10">
-        <v>200</v>
-      </c>
-      <c r="J206" s="11" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="2">
-        <v>48</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D207" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E207" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F207" s="4"/>
-      <c r="G207" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="I207" s="5">
-        <v>300</v>
-      </c>
-      <c r="J207" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="7">
-        <v>48</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="C208" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D208" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H208" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I208" s="10">
-        <v>200</v>
-      </c>
-      <c r="J208" s="11" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="2">
-        <v>48</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G209" s="4"/>
-      <c r="H209" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="I209" s="5">
-        <v>100</v>
-      </c>
-      <c r="J209" s="6" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="7">
-        <v>48</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G210" s="9"/>
-      <c r="H210" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="I210" s="10">
-        <v>200</v>
-      </c>
-      <c r="J210" s="11" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8683,7 +8676,7 @@
         <v>48</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>11</v>
@@ -8691,165 +8684,161 @@
       <c r="D211" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G211" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="E211" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F211" s="4"/>
+      <c r="G211" s="4"/>
       <c r="H211" s="2" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="I211" s="5">
         <v>300</v>
       </c>
       <c r="J211" s="6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="7">
+        <v>48</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="I212" s="10">
+        <v>300</v>
+      </c>
+      <c r="J212" s="11" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="2">
+        <v>48</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="4"/>
+      <c r="H213" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I213" s="5">
+        <v>200</v>
+      </c>
+      <c r="J213" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="7">
+        <v>48</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" s="9"/>
+      <c r="G214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I214" s="10">
+        <v>300</v>
+      </c>
+      <c r="J214" s="11" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="2">
+        <v>48</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="4"/>
+      <c r="E215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="4"/>
+      <c r="H215" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="I215" s="5">
+        <v>100</v>
+      </c>
+      <c r="J215" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="7">
+        <v>48</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
+      <c r="F216" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="9"/>
+      <c r="H216" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="I216" s="10">
+        <v>200</v>
+      </c>
+      <c r="J216" s="11" t="s">
         <v>551</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="2">
-        <v>48</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E212" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
-      <c r="H212" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="I212" s="5">
-        <v>300</v>
-      </c>
-      <c r="J212" s="6" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="7">
-        <v>48</v>
-      </c>
-      <c r="B213" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H213" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="I213" s="10">
-        <v>300</v>
-      </c>
-      <c r="J213" s="11" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="2">
-        <v>48</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D214" s="4"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G214" s="4"/>
-      <c r="H214" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="I214" s="5">
-        <v>200</v>
-      </c>
-      <c r="J214" s="6" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="7">
-        <v>48</v>
-      </c>
-      <c r="B215" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="C215" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D215" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F215" s="9"/>
-      <c r="G215" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H215" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I215" s="10">
-        <v>300</v>
-      </c>
-      <c r="J215" s="11" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="2">
-        <v>48</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D216" s="4"/>
-      <c r="E216" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F216" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G216" s="4"/>
-      <c r="H216" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="I216" s="5">
-        <v>100</v>
-      </c>
-      <c r="J216" s="6" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8857,393 +8846,395 @@
         <v>48</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9" t="s">
-        <v>11</v>
-      </c>
+      <c r="D217" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F217" s="9"/>
       <c r="G217" s="9"/>
       <c r="H217" s="7" t="s">
-        <v>477</v>
+        <v>553</v>
       </c>
       <c r="I217" s="10">
+        <v>500</v>
+      </c>
+      <c r="J217" s="11" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="2">
+        <v>48</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="4"/>
+      <c r="H218" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I218" s="5">
+        <v>300</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="7">
+        <v>48</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="9"/>
+      <c r="F219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="I219" s="10">
+        <v>500</v>
+      </c>
+      <c r="J219" s="11" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="2">
+        <v>48</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I220" s="5">
         <v>200</v>
       </c>
-      <c r="J217" s="11" t="s">
+      <c r="J220" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="7">
+        <v>48</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
+      <c r="F221" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="9"/>
+      <c r="H221" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="I221" s="10">
+        <v>200</v>
+      </c>
+      <c r="J221" s="11" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="2">
+        <v>48</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F222" s="4"/>
+      <c r="G222" s="4"/>
+      <c r="H222" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I222" s="5">
+        <v>200</v>
+      </c>
+      <c r="J222" s="6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="7">
+        <v>48</v>
+      </c>
+      <c r="B223" s="8" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="7">
+      <c r="C223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F223" s="9"/>
+      <c r="G223" s="9"/>
+      <c r="H223" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="I223" s="10">
+        <v>300</v>
+      </c>
+      <c r="J223" s="11" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="2">
         <v>48</v>
       </c>
-      <c r="B218" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D218" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E218" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F218" s="9"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="I218" s="10">
-        <v>500</v>
-      </c>
-      <c r="J218" s="11" t="s">
+      <c r="B224" s="3" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="2">
+      <c r="C224" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I224" s="5">
+        <v>200</v>
+      </c>
+      <c r="J224" s="6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="7">
         <v>48</v>
       </c>
-      <c r="B219" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D219" s="4"/>
-      <c r="E219" s="4"/>
-      <c r="F219" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G219" s="4"/>
-      <c r="H219" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I219" s="5">
+      <c r="B225" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="9"/>
+      <c r="F225" s="9"/>
+      <c r="G225" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I225" s="10">
+        <v>200</v>
+      </c>
+      <c r="J225" s="11" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="2">
+        <v>48</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F226" s="4"/>
+      <c r="G226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I226" s="5">
         <v>300</v>
       </c>
-      <c r="J219" s="6" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="7">
+      <c r="J226" s="6" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="7">
         <v>48</v>
       </c>
-      <c r="B220" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="C220" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D220" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" s="9"/>
-      <c r="F220" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G220" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H220" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="I220" s="10">
-        <v>500</v>
-      </c>
-      <c r="J220" s="11" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="2">
+      <c r="B227" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F227" s="9"/>
+      <c r="G227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I227" s="10">
+        <v>300</v>
+      </c>
+      <c r="J227" s="11" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="2">
         <v>48</v>
       </c>
-      <c r="B221" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D221" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G221" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="I221" s="5">
+      <c r="B228" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4"/>
+      <c r="G228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I228" s="5">
         <v>200</v>
       </c>
-      <c r="J221" s="6" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="7">
+      <c r="J228" s="6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="7">
         <v>48</v>
       </c>
-      <c r="B222" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="C222" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G222" s="9"/>
-      <c r="H222" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="I222" s="10">
+      <c r="B229" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="9"/>
+      <c r="F229" s="9"/>
+      <c r="G229" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="I229" s="10">
         <v>200</v>
       </c>
-      <c r="J222" s="11" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="2">
+      <c r="J229" s="11" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="2">
         <v>48</v>
       </c>
-      <c r="B223" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D223" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E223" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I223" s="5">
-        <v>200</v>
-      </c>
-      <c r="J223" s="6" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="7">
-        <v>48</v>
-      </c>
-      <c r="B224" s="8" t="s">
+      <c r="B230" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="C224" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D224" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F224" s="9"/>
-      <c r="G224" s="9"/>
-      <c r="H224" s="7" t="s">
+      <c r="C230" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
+      <c r="H230" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I230" s="5">
+        <v>300</v>
+      </c>
+      <c r="J230" s="6" t="s">
         <v>582</v>
-      </c>
-      <c r="I224" s="10">
-        <v>300</v>
-      </c>
-      <c r="J224" s="11" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="2">
-        <v>48</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D225" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H225" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I225" s="5">
-        <v>200</v>
-      </c>
-      <c r="J225" s="6" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="7">
-        <v>48</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D226" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E226" s="9"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H226" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I226" s="10">
-        <v>200</v>
-      </c>
-      <c r="J226" s="11" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="2">
-        <v>48</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D227" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E227" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F227" s="4"/>
-      <c r="G227" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I227" s="5">
-        <v>300</v>
-      </c>
-      <c r="J227" s="6" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="7">
-        <v>48</v>
-      </c>
-      <c r="B228" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F228" s="9"/>
-      <c r="G228" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H228" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I228" s="10">
-        <v>300</v>
-      </c>
-      <c r="J228" s="11" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="2">
-        <v>48</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
-      <c r="G229" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H229" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I229" s="5">
-        <v>200</v>
-      </c>
-      <c r="J229" s="6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="7">
-        <v>48</v>
-      </c>
-      <c r="B230" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="C230" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="9"/>
-      <c r="F230" s="9"/>
-      <c r="G230" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H230" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="I230" s="10">
-        <v>200</v>
-      </c>
-      <c r="J230" s="11" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9251,7 +9242,7 @@
         <v>48</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>11</v>
@@ -9265,13 +9256,13 @@
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="2" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="I231" s="5">
         <v>300</v>
       </c>
       <c r="J231" s="6" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9279,7 +9270,7 @@
         <v>48</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>11</v>
@@ -9293,13 +9284,13 @@
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="2" t="s">
-        <v>186</v>
+        <v>586</v>
       </c>
       <c r="I232" s="5">
         <v>300</v>
       </c>
       <c r="J232" s="6" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9307,7 +9298,7 @@
         <v>48</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>11</v>
@@ -9319,129 +9310,129 @@
         <v>11</v>
       </c>
       <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
+      <c r="G233" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="H233" s="2" t="s">
-        <v>601</v>
+        <v>183</v>
       </c>
       <c r="I233" s="5">
+        <v>500</v>
+      </c>
+      <c r="J233" s="6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="7">
+        <v>48</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F234" s="9"/>
+      <c r="G234" s="9"/>
+      <c r="H234" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="I234" s="10">
+        <v>100</v>
+      </c>
+      <c r="J234" s="11" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="2">
+        <v>48</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I235" s="5">
+        <v>200</v>
+      </c>
+      <c r="J235" s="6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="7">
+        <v>48</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="C236" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D236" s="9"/>
+      <c r="E236" s="9"/>
+      <c r="F236" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="9"/>
+      <c r="H236" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="I236" s="10">
+        <v>200</v>
+      </c>
+      <c r="J236" s="11" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="2">
+        <v>49</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4"/>
+      <c r="G237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I237" s="5">
         <v>300</v>
       </c>
-      <c r="J233" s="6" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="2">
-        <v>48</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D234" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E234" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I234" s="5">
-        <v>500</v>
-      </c>
-      <c r="J234" s="6" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="7">
-        <v>48</v>
-      </c>
-      <c r="B235" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D235" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E235" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F235" s="9"/>
-      <c r="G235" s="9"/>
-      <c r="H235" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="I235" s="10">
-        <v>100</v>
-      </c>
-      <c r="J235" s="11" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="2">
-        <v>48</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D236" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="I236" s="5">
-        <v>200</v>
-      </c>
-      <c r="J236" s="6" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="7">
-        <v>48</v>
-      </c>
-      <c r="B237" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G237" s="9"/>
-      <c r="H237" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="I237" s="10">
-        <v>200</v>
-      </c>
-      <c r="J237" s="11" t="s">
-        <v>611</v>
+      <c r="J237" s="6" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9449,7 +9440,7 @@
         <v>49</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>11</v>
@@ -9457,11 +9448,11 @@
       <c r="D238" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E238" s="4"/>
+      <c r="E238" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="F238" s="4"/>
-      <c r="G238" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="G238" s="4"/>
       <c r="H238" s="2" t="s">
         <v>154</v>
       </c>
@@ -9469,7 +9460,7 @@
         <v>300</v>
       </c>
       <c r="J238" s="6" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9477,7 +9468,7 @@
         <v>49</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>11</v>
@@ -9488,110 +9479,110 @@
       <c r="E239" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
+      <c r="F239" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="H239" s="2" t="s">
-        <v>154</v>
+        <v>602</v>
       </c>
       <c r="I239" s="5">
+        <v>500</v>
+      </c>
+      <c r="J239" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="7">
+        <v>49</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H240" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="I240" s="10">
         <v>300</v>
       </c>
-      <c r="J239" s="6" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="2">
+      <c r="J240" s="11" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="2">
         <v>49</v>
       </c>
-      <c r="B240" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D240" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E240" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F240" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G240" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="I240" s="5">
-        <v>500</v>
-      </c>
-      <c r="J240" s="6" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="7">
+      <c r="B241" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="I241" s="5">
+        <v>300</v>
+      </c>
+      <c r="J241" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="7">
         <v>49</v>
       </c>
-      <c r="B241" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D241" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F241" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G241" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H241" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="I241" s="10">
+      <c r="B242" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="C242" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="9"/>
+      <c r="F242" s="9"/>
+      <c r="G242" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I242" s="10">
         <v>300</v>
       </c>
-      <c r="J241" s="11" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2">
-        <v>49</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D242" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G242" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="I242" s="5">
-        <v>300</v>
-      </c>
-      <c r="J242" s="6" t="s">
-        <v>624</v>
+      <c r="J242" s="11" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9599,7 +9590,7 @@
         <v>49</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>11</v>
@@ -9613,365 +9604,365 @@
         <v>11</v>
       </c>
       <c r="H243" s="7" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="I243" s="10">
+        <v>200</v>
+      </c>
+      <c r="J243" s="11" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="2">
+        <v>49</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="4"/>
+      <c r="H244" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I244" s="5">
+        <v>200</v>
+      </c>
+      <c r="J244" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="7">
+        <v>49</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F245" s="9"/>
+      <c r="G245" s="9"/>
+      <c r="H245" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I245" s="10">
         <v>300</v>
       </c>
-      <c r="J243" s="11" t="s">
+      <c r="J245" s="11" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="2">
+        <v>49</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="4"/>
+      <c r="F246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="I246" s="5">
+        <v>300</v>
+      </c>
+      <c r="J246" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="7">
+        <v>49</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H247" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="I247" s="10">
+        <v>500</v>
+      </c>
+      <c r="J247" s="11" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="2">
+        <v>49</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F248" s="4"/>
+      <c r="G248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="I248" s="5">
+        <v>500</v>
+      </c>
+      <c r="J248" s="6" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="7">
+    <row r="249" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="7">
         <v>49</v>
       </c>
-      <c r="B244" s="8" t="s">
+      <c r="B249" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="C244" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D244" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E244" s="9"/>
-      <c r="F244" s="9"/>
-      <c r="G244" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H244" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I244" s="10">
-        <v>200</v>
-      </c>
-      <c r="J244" s="11" t="s">
+      <c r="C249" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D249" s="9"/>
+      <c r="E249" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F249" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="9"/>
+      <c r="H249" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="I249" s="10">
+        <v>300</v>
+      </c>
+      <c r="J249" s="11" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="2">
+    <row r="250" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="2">
         <v>49</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B250" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C245" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G245" s="4"/>
-      <c r="H245" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I245" s="5">
-        <v>200</v>
-      </c>
-      <c r="J245" s="6" t="s">
+      <c r="C250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H250" s="2" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="7">
+      <c r="I250" s="5">
+        <v>500</v>
+      </c>
+      <c r="J250" s="6" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="7">
         <v>49</v>
       </c>
-      <c r="B246" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="C246" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D246" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E246" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F246" s="9"/>
-      <c r="G246" s="9"/>
-      <c r="H246" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I246" s="10">
+      <c r="B251" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F251" s="9"/>
+      <c r="G251" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H251" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I251" s="10">
+        <v>500</v>
+      </c>
+      <c r="J251" s="11" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="2">
+        <v>49</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F252" s="4"/>
+      <c r="G252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H252" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="I252" s="5">
+        <v>500</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="7">
+        <v>49</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E253" s="9"/>
+      <c r="F253" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="I253" s="10">
+        <v>500</v>
+      </c>
+      <c r="J253" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="2">
+        <v>49</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F254" s="4"/>
+      <c r="G254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="I254" s="5">
+        <v>500</v>
+      </c>
+      <c r="J254" s="6" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="7">
+        <v>49</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="9"/>
+      <c r="F255" s="9"/>
+      <c r="G255" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H255" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I255" s="10">
         <v>300</v>
       </c>
-      <c r="J246" s="11" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="2">
-        <v>49</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D247" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E247" s="4"/>
-      <c r="F247" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G247" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="I247" s="5">
-        <v>300</v>
-      </c>
-      <c r="J247" s="6" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="7">
-        <v>49</v>
-      </c>
-      <c r="B248" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="C248" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D248" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E248" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F248" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G248" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H248" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="I248" s="10">
-        <v>500</v>
-      </c>
-      <c r="J248" s="11" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="2">
-        <v>49</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D249" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E249" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="I249" s="5">
-        <v>500</v>
-      </c>
-      <c r="J249" s="6" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="7">
-        <v>49</v>
-      </c>
-      <c r="B250" s="8" t="s">
+      <c r="J255" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="C250" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F250" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G250" s="9"/>
-      <c r="H250" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="I250" s="10">
-        <v>300</v>
-      </c>
-      <c r="J250" s="11" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="2">
-        <v>49</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D251" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G251" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="I251" s="5">
-        <v>500</v>
-      </c>
-      <c r="J251" s="6" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="7">
-        <v>49</v>
-      </c>
-      <c r="B252" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="C252" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D252" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E252" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F252" s="9"/>
-      <c r="G252" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H252" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I252" s="10">
-        <v>500</v>
-      </c>
-      <c r="J252" s="11" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="2">
-        <v>49</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E253" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F253" s="4"/>
-      <c r="G253" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H253" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="I253" s="5">
-        <v>500</v>
-      </c>
-      <c r="J253" s="6" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="7">
-        <v>49</v>
-      </c>
-      <c r="B254" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C254" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D254" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E254" s="9"/>
-      <c r="F254" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G254" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H254" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="I254" s="10">
-        <v>500</v>
-      </c>
-      <c r="J254" s="11" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="2">
-        <v>49</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D255" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E255" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F255" s="4"/>
-      <c r="G255" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="I255" s="5">
-        <v>500</v>
-      </c>
-      <c r="J255" s="6" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9979,7 +9970,7 @@
         <v>49</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>11</v>
@@ -9987,227 +9978,199 @@
       <c r="D256" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E256" s="9"/>
+      <c r="E256" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="F256" s="9"/>
       <c r="G256" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H256" s="7" t="s">
-        <v>202</v>
+        <v>644</v>
       </c>
       <c r="I256" s="10">
         <v>300</v>
       </c>
       <c r="J256" s="11" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="2">
+        <v>49</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="I257" s="5">
+        <v>300</v>
+      </c>
+      <c r="J257" s="6" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="7">
+        <v>49</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F258" s="9"/>
+      <c r="G258" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="I258" s="10">
+        <v>500</v>
+      </c>
+      <c r="J258" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="2">
+        <v>49</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="4"/>
+      <c r="F259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I259" s="5">
+        <v>300</v>
+      </c>
+      <c r="J259" s="6" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="7">
+        <v>49</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D260" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F260" s="9"/>
+      <c r="G260" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I260" s="10">
+        <v>500</v>
+      </c>
+      <c r="J260" s="11" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="2">
+        <v>49</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F261" s="4"/>
+      <c r="G261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I261" s="5">
+        <v>500</v>
+      </c>
+      <c r="J261" s="6" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="7">
+    <row r="262" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="7">
         <v>49</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B262" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="C257" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D257" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E257" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F257" s="9"/>
-      <c r="G257" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H257" s="7" t="s">
+      <c r="C262" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D262" s="9"/>
+      <c r="E262" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F262" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="9"/>
+      <c r="H262" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I262" s="10">
+        <v>200</v>
+      </c>
+      <c r="J262" s="11" t="s">
         <v>659</v>
-      </c>
-      <c r="I257" s="10">
-        <v>300</v>
-      </c>
-      <c r="J257" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="2">
-        <v>49</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D258" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G258" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="I258" s="5">
-        <v>300</v>
-      </c>
-      <c r="J258" s="6" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="7">
-        <v>49</v>
-      </c>
-      <c r="B259" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="C259" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D259" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E259" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F259" s="9"/>
-      <c r="G259" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H259" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="I259" s="10">
-        <v>500</v>
-      </c>
-      <c r="J259" s="11" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="2">
-        <v>49</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D260" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G260" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H260" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I260" s="5">
-        <v>300</v>
-      </c>
-      <c r="J260" s="6" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="7">
-        <v>49</v>
-      </c>
-      <c r="B261" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="C261" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E261" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F261" s="9"/>
-      <c r="G261" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H261" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I261" s="10">
-        <v>500</v>
-      </c>
-      <c r="J261" s="11" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="2">
-        <v>49</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D262" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E262" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F262" s="4"/>
-      <c r="G262" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H262" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="I262" s="5">
-        <v>500</v>
-      </c>
-      <c r="J262" s="6" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="7">
-        <v>49</v>
-      </c>
-      <c r="B263" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="C263" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F263" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G263" s="9"/>
-      <c r="H263" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I263" s="10">
-        <v>200</v>
-      </c>
-      <c r="J263" s="11" t="s">
-        <v>674</v>
       </c>
     </row>
   </sheetData>
